--- a/结果/2.分类结果/一位码/已分类_一位码_苏教版_6.1_六年级上_独立职业.xlsx
+++ b/结果/2.分类结果/一位码/已分类_一位码_苏教版_6.1_六年级上_独立职业.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,14 +495,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -510,7 +512,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>教师</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -520,7 +522,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -529,32 +531,34 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>教师</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -563,18 +567,20 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -583,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -599,20 +605,22 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科学家</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,36 +630,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -661,56 +671,60 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>科学家</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -719,7 +733,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -733,18 +747,20 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -763,22 +779,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -801,22 +819,24 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -831,22 +851,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -855,7 +877,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -865,26 +887,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>教师</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -894,27 +918,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -923,7 +949,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -939,25 +965,27 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -967,22 +995,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -991,7 +1021,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1007,25 +1037,27 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1035,31 +1067,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1069,56 +1103,60 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>教师</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1127,12 +1165,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1143,16 +1181,18 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1161,7 +1201,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1177,16 +1217,18 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1200,27 +1242,29 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1234,31 +1278,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>邪教教主</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1268,31 +1314,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1302,31 +1350,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1341,90 +1391,96 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1443,22 +1499,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1467,36 +1525,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>售货员</t>
+          <t>邪教教主</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1506,70 +1566,74 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>顾客</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1579,22 +1643,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1608,7 +1674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1619,84 +1685,90 @@
       <c r="F35" t="n">
         <v>1</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>学生记者</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>被采访的长辈</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>2</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1719,18 +1791,20 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1739,12 +1813,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1753,27 +1827,29 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>农民</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1783,26 +1859,28 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>售货员</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1812,36 +1890,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1851,31 +1931,33 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>顾客</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1885,26 +1967,28 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>村官</t>
+          <t>顾客</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1914,65 +1998,69 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生记者</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1982,36 +2070,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>村干部</t>
+          <t>被采访的长辈</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2021,26 +2111,28 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>9</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>非从业人员-家庭角色</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>被采访的长辈</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2050,61 +2142,65 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>非从业人员-家庭角色</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2118,7 +2214,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2129,16 +2225,18 @@
       <c r="F50" t="n">
         <v>2</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2163,30 +2261,32 @@
       <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>村官</t>
+          <t>农民</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2197,20 +2297,22 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>农、林、牧、渔业生产及辅助人员</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>村民或记者</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2225,22 +2327,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2249,7 +2353,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2265,25 +2369,27 @@
       <c r="F54" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2299,20 +2405,22 @@
       <c r="F55" t="n">
         <v>1</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>村干部代表</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2322,36 +2430,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>村官</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2361,65 +2471,69 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>选举工作人员</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2429,31 +2543,33 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>居委会主任</t>
+          <t>村干部</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2469,20 +2585,22 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2492,61 +2610,65 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>电工</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2571,16 +2693,18 @@
       <c r="F63" t="n">
         <v>2</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2589,12 +2713,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2605,54 +2729,58 @@
       <c r="F64" t="n">
         <v>1</v>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>登山者</t>
+          <t>村官</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>村民或记者</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2662,27 +2790,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2707,59 +2837,63 @@
       <c r="F67" t="n">
         <v>1</v>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>民族英雄</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>村干部代表</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2769,31 +2903,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>病人</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2803,65 +2939,69 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>农、林、牧、渔业生产及辅助人员</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>农、林、牧、渔业生产及辅助人员</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>政治人物（总理）</t>
+          <t>选举工作人员</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2877,16 +3017,18 @@
       <c r="F72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>办事人员和有关人员</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2895,7 +3037,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2909,27 +3051,29 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>僧人</t>
+          <t>居委会主任</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2939,31 +3083,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>公主</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2973,26 +3119,28 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>取经人 / 神话人物</t>
+          <t>电工</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3007,26 +3155,28 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>生产制造及有关人员</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>僧人</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3036,27 +3186,29 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3065,12 +3217,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3081,88 +3233,94 @@
       <c r="F78" t="n">
         <v>1</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>宗教人物（佛教创始人）</t>
+          <t>登山者</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>舞蹈演员</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>诗人、作家、艺术家</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3172,31 +3330,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>民族英雄</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3206,7 +3366,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3215,22 +3375,24 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3245,26 +3407,28 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>病人</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3274,27 +3438,29 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3303,7 +3469,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3319,20 +3485,22 @@
       <c r="F85" t="n">
         <v>1</v>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>制作木乃伊的工匠</t>
+          <t>政治人物（总理）</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3347,31 +3515,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3381,26 +3551,28 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>僧人</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3415,128 +3587,136 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>工匠或石匠</t>
+          <t>公主</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>古希腊仪式参与者</t>
+          <t>取经人 / 神话人物</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>3</v>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>8</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>古希腊祭司或仪式参与者</t>
+          <t>僧人</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>古希腊人</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3546,31 +3726,33 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>哲学家</t>
+          <t>宗教人物（佛教创始人）</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3591,30 +3773,32 @@
       <c r="F93" t="n">
         <v>1</v>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>8</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>动物角色</t>
+          <t>舞蹈演员</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3623,22 +3807,24 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>诗人、作家、艺术家</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3653,31 +3839,33 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>运动员（古希腊）</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3687,22 +3875,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3711,7 +3901,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3725,22 +3915,24 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>10</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3755,22 +3947,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3779,7 +3973,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3789,22 +3983,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>10</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3813,7 +4009,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3827,52 +4023,56 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>志愿者</t>
+          <t>制作木乃伊的工匠</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>生产制造及有关人员</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3881,7 +4081,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3891,128 +4091,136 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>10</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>拟人化天气符号</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>工匠或石匠</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>6</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>生产制造及有关人员</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>古希腊仪式参与者</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>古希腊祭司或仪式参与者</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4022,65 +4230,69 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="G106" t="n">
+        <v>8</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>古希腊人</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G107" t="n">
+        <v>10</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>渔民</t>
+          <t>哲学家</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4090,31 +4302,33 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>工作场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>动物角色</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4129,60 +4343,64 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G109" t="n">
+        <v>10</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>运动员（古希腊）</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4197,22 +4415,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="G111" t="n">
+        <v>4</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4231,26 +4451,28 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="G112" t="n">
+        <v>10</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4265,26 +4487,28 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="G113" t="n">
+        <v>9</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>非从业人员-家庭角色</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4294,36 +4518,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F114" t="n">
         <v>2</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4333,26 +4559,28 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>7</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>志愿者</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4362,7 +4590,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4371,29 +4599,31 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G116" t="n">
+        <v>8</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>志愿者</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>插图</t>
@@ -4407,20 +4637,22 @@
       <c r="F117" t="n">
         <v>1</v>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="G117" t="n">
+        <v>8</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>圣诞节人物（象征形象）</t>
+          <t>志愿者</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4435,26 +4667,28 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="n">
+        <v>8</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4464,31 +4698,33 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>10</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>表演者</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4507,32 +4743,34 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>传说人物</t>
+          <t>拟人化天气符号</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4541,22 +4779,24 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G121" t="n">
+        <v>10</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>合唱团成员</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4566,61 +4806,65 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>5</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F123" t="n">
         <v>1</v>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="G123" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -4634,31 +4878,33 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4668,31 +4914,33 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F125" t="n">
         <v>1</v>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="G125" t="n">
+        <v>10</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>教师</t>
+          <t>渔民</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4702,38 +4950,40 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>工作场所</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>1</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="G126" t="n">
+        <v>5</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>农、林、牧、渔业生产及辅助人员</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>女</t>
-        </is>
-      </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>插图</t>
@@ -4741,31 +4991,33 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4775,31 +5027,33 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F128" t="n">
         <v>2</v>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>运动员</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4809,56 +5063,60 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>家庭</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>8</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4881,22 +5139,24 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>教师</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4906,7 +5166,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4917,16 +5177,18 @@
       <c r="F132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4940,27 +5202,29 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>学校</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>4</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4979,22 +5243,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F134" t="n">
         <v>3</v>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -5013,31 +5279,33 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>警察</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>女</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5051,66 +5319,70 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>4</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>男</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>插图</t>
+          <t>插图和文本</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>民权运动领袖</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>未知</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5121,20 +5393,22 @@
       <c r="F138" t="n">
         <v>1</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
+      <c r="G138" t="n">
+        <v>10</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>美国总统</t>
+          <t>圣诞节人物（象征形象）</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5144,57 +5418,1141 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>插图和文本</t>
+          <t>插图</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>公共场所</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>1</v>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr"/>
+      <c r="G139" t="n">
+        <v>8</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
+        <v>104</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>104</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>表演者</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="n">
+        <v>4</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>105</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>传说人物</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="n">
+        <v>8</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>不便分类的其他从业人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>105</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>合唱团成员</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>3</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>105</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>合唱团成员</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>106</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>107</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>107</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>108</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>108</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>教师</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>108</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>108</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>108</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>9</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>非从业人员-家庭角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>109</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>2</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>109</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>运动员</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>8</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>社会生产服务和生活服务人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>110</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>3</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>111</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>111</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>112</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>教师</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>113</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>113</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>3</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>非从业人员-学生/儿童</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>113</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>113</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="n">
+        <v>10</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>114</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>10</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>114</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>2</v>
+      </c>
+      <c r="G164" t="n">
+        <v>9</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>非从业人员-家庭角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>114</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>警察</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>4</v>
+      </c>
+      <c r="G165" t="n">
+        <v>3</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>办事人员和有关人员</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>115</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>10</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>115</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="n">
+        <v>10</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>115</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>民权运动领袖</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>115</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>美国总统</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>插图和文本</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>公共场所</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>党的机关、国家机关、群众团体和社会组织、企事业单位负责人</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
         <v>116</v>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>插图</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>插图</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>匹配失败</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>10</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>非从业人员-其他</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
